--- a/data/merged/2026-09-23/MERGED_UK_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_UK_Mite-Vacuum_2026-09-23.xlsx
@@ -1455,7 +1455,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1499,7 +1499,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1719,7 +1719,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1763,7 +1763,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1807,7 +1807,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1851,7 +1851,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -1874,50 +1874,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Product 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2259,7 +2215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR15"/>
+  <dimension ref="A1:BR14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2886,7 +2842,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -2899,23 +2855,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>OSALADI 3pcs Vacuum Wall Support Plastic Vacuum Holder for Wall Mounted Use Cordless Accessories Supports for Home Cleaning</t>
+          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine wi</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -2931,13 +2887,19 @@
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
       <c r="Y4"/>
-      <c r="Z4" s="19"/>
+      <c r="Z4" s="19">
+        <v>21.68</v>
+      </c>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
-      <c r="AD4" s="20"/>
+      <c r="AD4" s="20">
+        <v>87</v>
+      </c>
       <c r="AE4"/>
-      <c r="AF4" s="21"/>
+      <c r="AF4" s="21">
+        <v>3.9</v>
+      </c>
       <c r="AG4" s="22">
         <v>0</v>
       </c>
@@ -2988,7 +2950,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
+          <t>B0DHL35LFT</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -3001,23 +2963,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine wi</t>
+          <t>Jimmy BX7 Pro Max Mattress &amp; Bed Vacuum Cleaner 700W Power 15kPa Suction with UV-C Light 65°C Heat &amp; Graphene Tech, Dust Mite</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
+          <t>B0DHL35LFT</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -3033,18 +2995,16 @@
       <c r="W5" s="15"/>
       <c r="X5" s="15"/>
       <c r="Y5"/>
-      <c r="Z5" s="19">
-        <v>21.68</v>
-      </c>
+      <c r="Z5" s="19"/>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="20">
-        <v>87</v>
+        <v>358</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="21">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AG5" s="22">
         <v>0</v>
@@ -3096,7 +3056,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0DHL35LFT</t>
+          <t>B0DSCSR4MB</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -3109,23 +3069,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Jimmy BX7 Pro Max Mattress &amp; Bed Vacuum Cleaner 700W Power 15kPa Suction with UV-C Light 65°C Heat &amp; Graphene Tech, Dust Mite</t>
+          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; SofasMite Level Display, UV-C Light &amp; Hot Air &amp; Roller</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0DHL35LFT</t>
+          <t>B0DSCSR4MB</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -3146,11 +3106,11 @@
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="20">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG6" s="22">
         <v>0</v>
@@ -3202,7 +3162,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -3215,23 +3175,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; SofasMite Level Display, UV-C Light &amp; Hot Air &amp; Roller</t>
+          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -3252,11 +3212,11 @@
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="20">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG7" s="22">
         <v>0</v>
@@ -3308,7 +3268,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0DTS8VCFB</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -3321,23 +3281,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, He</t>
+          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; SofasUltrasonic Cleaning, UV-C Light &amp; Hot Air &amp; Roller</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0DTS8VCFB</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -3358,11 +3318,11 @@
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG8" s="22">
         <v>0</v>
@@ -3414,7 +3374,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0F13NCPTZ</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -3427,23 +3387,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; SofasUltrasonic Cleaning, UV-C Light &amp; Hot Air &amp; Roller</t>
+          <t>Bear Mattress Vacuum Cleaner, 15Kpa Suction &amp; 253.7nm UV-C Lamp Sterilization 5 in 1 Handheld Dust Mite Vacuum Cleaner, HEPA</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0F13NCPTZ</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -3464,7 +3424,7 @@
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="20">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="21">
@@ -3520,7 +3480,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0F13NCPTZ</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -3533,23 +3493,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Bear Mattress Vacuum Cleaner, 15Kpa Suction &amp; 253.7nm UV-C Lamp Sterilization 5 in 1 Handheld Dust Mite Vacuum Cleaner, HEPA</t>
+          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0F13NCPTZ</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -3570,7 +3530,7 @@
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>199</v>
+        <v>381</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
@@ -3626,7 +3586,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FBH3FKJH</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -3639,23 +3599,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen</t>
+          <t>Hoover HMC5 4-in-1 Mattress Vacuum Cleaner, Anti-Allergen [HMC520UV]sHandheld Dust Mite Vacuum Cleaner for beds and sofas -</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FBH3FKJH</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -3671,16 +3631,18 @@
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
       <c r="Y11"/>
-      <c r="Z11" s="19"/>
+      <c r="Z11" s="19">
+        <v>74.17</v>
+      </c>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>381</v>
+        <v>534</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
@@ -3732,7 +3694,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0FBH3FKJH</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -3745,23 +3707,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Hoover HMC5 4-in-1 Mattress Vacuum Cleaner, Anti-Allergen [HMC520UV]sHandheld Dust Mite Vacuum Cleaner for beds and sofas -</t>
+          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0FBH3FKJH</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -3777,14 +3739,12 @@
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12"/>
-      <c r="Z12" s="19">
-        <v>74.17</v>
-      </c>
+      <c r="Z12" s="19"/>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>534</v>
+        <v>192</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
@@ -3840,7 +3800,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0GBYBRVJM</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -3853,23 +3813,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500</t>
+          <t>Teant Mattress Bed Vacuum Cleaner, 16 kPa Suction &amp; 253.7nm UV-C, MV-BLUEs2-Speed Mattress Vacuum with 33000 RPM Tapping, U</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GBYBRVJM?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0GBYBRVJM</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -3890,11 +3850,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
@@ -3946,7 +3906,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0GBYBRVJM</t>
+          <t>B0GJDH8XTW</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -3959,23 +3919,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Teant Mattress Bed Vacuum Cleaner, 16 kPa Suction &amp; 253.7nm UV-C, MV-BLUEs2-Speed Mattress Vacuum with 33000 RPM Tapping, U</t>
+          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights,</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GBYBRVJM?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0GBYBRVJM</t>
+          <t>B0GJDH8XTW</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -3996,11 +3956,11 @@
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
@@ -4045,112 +4005,6 @@
       <c r="BQ14" s="23"/>
       <c r="BR14"/>
     </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>B0GJDH8XTW</t>
-        </is>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights,</t>
-        </is>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
-        </is>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>B0GJDH8XTW</t>
-        </is>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15"/>
-      <c r="AB15"/>
-      <c r="AC15"/>
-      <c r="AD15" s="20">
-        <v>30</v>
-      </c>
-      <c r="AE15"/>
-      <c r="AF15" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG15" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH15"/>
-      <c r="AI15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ15"/>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="20"/>
-      <c r="AM15"/>
-      <c r="AN15" s="13"/>
-      <c r="AO15" s="13"/>
-      <c r="AP15"/>
-      <c r="AQ15" s="20"/>
-      <c r="AR15"/>
-      <c r="AS15"/>
-      <c r="AT15"/>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="14"/>
-      <c r="AW15" s="13"/>
-      <c r="AX15" s="13"/>
-      <c r="AY15" s="13"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
-      <c r="BB15" s="13"/>
-      <c r="BC15" s="13"/>
-      <c r="BD15" s="13"/>
-      <c r="BE15" s="13"/>
-      <c r="BF15" s="13"/>
-      <c r="BG15" s="13"/>
-      <c r="BH15" s="14"/>
-      <c r="BI15"/>
-      <c r="BJ15"/>
-      <c r="BK15" s="23"/>
-      <c r="BL15"/>
-      <c r="BM15" s="23"/>
-      <c r="BN15"/>
-      <c r="BO15" s="23"/>
-      <c r="BP15"/>
-      <c r="BQ15" s="23"/>
-      <c r="BR15"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4165,68 +4019,63 @@
     <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V?psc=1"/>
     <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PNQ3QEyHL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.co.uk/dp/B0D1QQXH6V"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41-H5-VQSVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BhZB73+YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Vef2rJE5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.co.uk/dp/B0DHL35LFT"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bpuKTUQQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/616ONjp63mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/612vIVIFq3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.uk/dp/B0F13NCPTZ"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7185wuCbHrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mCoX81GcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0FBH3FKJH"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TSFHQeA7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B0GBYBRVJM"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
-    <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711M2XsW1sL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
   </hyperlinks>
-  <drawing r:id="rId71"/>
+  <drawing r:id="rId66"/>
 </worksheet>
 </file>
 
